--- a/Proyecto Interno/review-food-security-paper/07_tables/final/tab02_premium_median.xlsx
+++ b/Proyecto Interno/review-food-security-paper/07_tables/final/tab02_premium_median.xlsx
@@ -38,217 +38,217 @@
     <t xml:space="preserve">2019–2024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.845 (1.798, 1.967)</t>
+    <t xml:space="preserve">1.872 (1.825, 2.000)</t>
   </si>
   <si>
     <t xml:space="preserve">2.805 (2.744, 3.022)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.518 (1.505, 1.537)</t>
+    <t xml:space="preserve">1.498 (1.488, 1.511)</t>
   </si>
   <si>
     <t xml:space="preserve">2019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.720 (1.712, 1.738)</t>
+    <t xml:space="preserve">1.728 (1.720, 1.751)</t>
   </si>
   <si>
     <t xml:space="preserve">2.572 (2.558, 2.631)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.499 (1.488, 1.505)</t>
+    <t xml:space="preserve">1.491 (1.481, 1.497)</t>
   </si>
   <si>
     <t xml:space="preserve">2020</t>
   </si>
   <si>
-    <t xml:space="preserve">1.811 (1.795, 1.822)</t>
+    <t xml:space="preserve">1.826 (1.811, 1.837)</t>
   </si>
   <si>
     <t xml:space="preserve">2.785 (2.745, 2.798)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.528 (1.522, 1.540)</t>
+    <t xml:space="preserve">1.515 (1.508, 1.526)</t>
   </si>
   <si>
     <t xml:space="preserve">2021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.877 (1.864, 1.902)</t>
+    <t xml:space="preserve">1.898 (1.884, 1.920)</t>
   </si>
   <si>
     <t xml:space="preserve">2.838 (2.812, 2.852)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.506 (1.501, 1.510)</t>
+    <t xml:space="preserve">1.488 (1.485, 1.495)</t>
   </si>
   <si>
     <t xml:space="preserve">2022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.875 (1.833, 1.954)</t>
+    <t xml:space="preserve">1.904 (1.864, 1.987)</t>
   </si>
   <si>
     <t xml:space="preserve">2.820 (2.765, 2.976)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.515 (1.505, 1.518)</t>
+    <t xml:space="preserve">1.487 (1.482, 1.494)</t>
   </si>
   <si>
     <t xml:space="preserve">2023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.827 (1.799, 2.041)</t>
+    <t xml:space="preserve">1.871 (1.840, 2.087)</t>
   </si>
   <si>
     <t xml:space="preserve">2.812 (2.760, 3.130)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.534 (1.524, 1.542)</t>
+    <t xml:space="preserve">1.500 (1.491, 1.505)</t>
   </si>
   <si>
     <t xml:space="preserve">2024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.370 (2.292, 2.382)</t>
+    <t xml:space="preserve">2.407 (2.332, 2.421)</t>
   </si>
   <si>
     <t xml:space="preserve">3.716 (3.552, 3.728)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.562 (1.549, 1.569)</t>
+    <t xml:space="preserve">1.537 (1.523, 1.544)</t>
   </si>
   <si>
     <t xml:space="preserve">Medellín</t>
   </si>
   <si>
-    <t xml:space="preserve">2.010 (1.962, 2.109)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.835 (2.790, 2.977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.415 (1.404, 1.432)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.828 (1.817, 1.883)</t>
+    <t xml:space="preserve">2.028 (1.973, 2.128)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.835 (2.790, 2.973)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.402 (1.394, 1.415)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.837 (1.825, 1.891)</t>
   </si>
   <si>
     <t xml:space="preserve">2.581 (2.555, 2.615)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.403 (1.398, 1.413)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.985 (1.941, 1.993)</t>
+    <t xml:space="preserve">1.397 (1.391, 1.406)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.995 (1.953, 2.005)</t>
   </si>
   <si>
     <t xml:space="preserve">2.811 (2.799, 2.824)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.412 (1.405, 1.423)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.012 (2.004, 2.029)</t>
+    <t xml:space="preserve">1.404 (1.396, 1.415)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.028 (2.020, 2.044)</t>
   </si>
   <si>
     <t xml:space="preserve">2.836 (2.814, 2.861)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.408 (1.406, 1.413)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.085 (2.037, 2.129)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.968 (2.898, 3.051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.428 (1.419, 1.436)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.975 (1.972, 2.070)</t>
+    <t xml:space="preserve">1.397 (1.395, 1.402)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.107 (2.059, 2.151)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.965 (2.898, 3.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.413 (1.401, 1.420)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.006 (2.003, 2.107)</t>
   </si>
   <si>
     <t xml:space="preserve">2.831 (2.805, 2.899)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.423 (1.400, 1.428)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.425 (2.383, 2.456)</t>
+    <t xml:space="preserve">1.400 (1.376, 1.406)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.455 (2.411, 2.486)</t>
   </si>
   <si>
     <t xml:space="preserve">3.518 (3.375, 3.548)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.439 (1.416, 1.447)</t>
+    <t xml:space="preserve">1.421 (1.400, 1.430)</t>
   </si>
   <si>
     <t xml:space="preserve">Cali</t>
   </si>
   <si>
-    <t xml:space="preserve">1.986 (1.914, 2.138)</t>
+    <t xml:space="preserve">1.991 (1.915, 2.152)</t>
   </si>
   <si>
     <t xml:space="preserve">2.801 (2.749, 3.080)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.428 (1.411, 1.456)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.825 (1.803, 1.876)</t>
+    <t xml:space="preserve">1.430 (1.403, 1.446)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.819 (1.798, 1.868)</t>
   </si>
   <si>
     <t xml:space="preserve">2.607 (2.573, 2.678)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.428 (1.423, 1.432)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.923 (1.893, 1.945)</t>
+    <t xml:space="preserve">1.433 (1.426, 1.437)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.919 (1.896, 1.943)</t>
   </si>
   <si>
     <t xml:space="preserve">2.756 (2.746, 2.791)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.430 (1.421, 1.461)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.972 (1.946, 1.986)</t>
+    <t xml:space="preserve">1.437 (1.422, 1.455)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.976 (1.946, 1.990)</t>
   </si>
   <si>
     <t xml:space="preserve">2.776 (2.763, 2.809)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.426 (1.403, 1.444)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.039 (1.995, 2.080)</t>
+    <t xml:space="preserve">1.425 (1.401, 1.442)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.054 (2.008, 2.102)</t>
   </si>
   <si>
     <t xml:space="preserve">2.882 (2.787, 3.028)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.416 (1.410, 1.441)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.024 (1.993, 2.248)</t>
+    <t xml:space="preserve">1.408 (1.398, 1.426)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.053 (2.025, 2.269)</t>
   </si>
   <si>
     <t xml:space="preserve">2.974 (2.844, 3.148)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.419 (1.401, 1.449)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.574 (2.501, 2.614)</t>
+    <t xml:space="preserve">1.401 (1.389, 1.429)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.596 (2.555, 2.635)</t>
   </si>
   <si>
     <t xml:space="preserve">3.805 (3.691, 3.867)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.470 (1.457, 1.486)</t>
+    <t xml:space="preserve">1.454 (1.436, 1.469)</t>
   </si>
   <si>
     <t xml:space="preserve">Note: Median (Q1, Q3) across monthly observations. Premiums computed from real COP, deflated by city-level food CPI (DANE División 01100000, base: December 2018).</t>
